--- a/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
+++ b/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9cdab296632f4a21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R55f0903a45bb41ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R7374c81f92a346ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="Rfd8aa52aca1b43b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Rdc5b23efd3f649e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="Re7e4137e90604ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="Rd86ac98797d642b1"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rbd362f6addd44026"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R9eb53fffc9064d4d"/>
+    <ns0:sheet name="02_API一覧" sheetId="3" ns1:id="R86e00ae799ef494d"/>
+    <ns0:sheet name="03_APIインターフェース" sheetId="4" ns1:id="Rf55b0440415748c1"/>
+    <ns0:sheet name="04_処理業務フロー" sheetId="5" ns1:id="Rf7ae336968ff42ac"/>
+    <ns0:sheet name="05_SQL_Parameter" sheetId="6" ns1:id="R6ecf54ead0c74a56"/>
+    <ns0:sheet name="06_単体テスト観点" sheetId="7" ns1:id="R957b792507654bd0"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="21">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -133,6 +133,11 @@
       <x:sz val="11"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172B40"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
   <x:fills count="12">
     <x:fill>
@@ -192,7 +197,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="32">
+  <x:borders count="33">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -442,11 +447,25 @@
         <x:color rgb="FFD9E2F3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="213">
+  <x:cellXfs count="215">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,6 +1085,12 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1687,7 +1712,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="F15" s="146" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="G15" s="146" t="str">
         <x:v>Ver.2.1</x:v>
@@ -1717,7 +1742,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="F16" s="146" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="G16" s="146" t="str">
         <x:v>2026-09-28</x:v>
@@ -2085,7 +2110,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -2280,15 +2305,31 @@
       <x:c r="K10" s="156"/>
       <x:c r="L10" s="156"/>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="156"/>
-      <x:c r="B11" s="156"/>
-      <x:c r="C11" s="156"/>
-      <x:c r="D11" s="156"/>
-      <x:c r="E11" s="156"/>
-      <x:c r="F11" s="156"/>
-      <x:c r="G11" s="156"/>
-      <x:c r="H11" s="156"/>
+    <x:row r="11" ht="75" customHeight="1">
+      <x:c r="A11" s="214" t="str">
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B11" s="214" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C11" s="214" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D11" s="214" t="str">
+        <x:v>CHG-DB-20260929-01：参照Columnの注記を物理外鍵なしへ統一。認証処理/SQL/応答契約は変更なし。</x:v>
+      </x:c>
+      <x:c r="E11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H11" s="214" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
       <x:c r="I11" s="156"/>
       <x:c r="J11" s="156"/>
       <x:c r="K11" s="156"/>
@@ -3496,7 +3537,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -5216,7 +5257,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -8263,7 +8304,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -11372,7 +11413,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -12023,7 +12064,7 @@
         <x:v>同一Transaction</x:v>
       </x:c>
       <x:c r="I24" s="73" t="str">
-        <x:v>user_roles.user_id等FK/UK</x:v>
+        <x:v>user_roles.user_id等の論理参照/UK</x:v>
       </x:c>
       <x:c r="J24" s="73" t="str">
         <x:v>認証対象User</x:v>
@@ -12213,7 +12254,7 @@
       </x:c>
       <x:c r="L29" s="2"/>
     </x:row>
-    <x:row r="30" ht="90" hidden="0" customHeight="1">
+    <x:row r="30" ht="65" hidden="0" customHeight="1">
       <x:c r="A30" s="73" t="str">
         <x:v>SQL-07</x:v>
       </x:c>
@@ -12236,10 +12277,10 @@
         <x:v>SQL-01.id、不存在はnull</x:v>
       </x:c>
       <x:c r="H30" s="73" t="str">
-        <x:v>存在しないUserのFK値を捏造しない</x:v>
+        <x:v>存在しないUser IDを記録しない。取得できない場合はNULL。</x:v>
       </x:c>
       <x:c r="I30" s="73" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照（物理外鍵なし）</x:v>
       </x:c>
       <x:c r="J30" s="73" t="str">
         <x:v>認証対象</x:v>
@@ -18275,7 +18316,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>

--- a/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
+++ b/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rbd362f6addd44026"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R9eb53fffc9064d4d"/>
-    <ns0:sheet name="02_API一覧" sheetId="3" ns1:id="R86e00ae799ef494d"/>
-    <ns0:sheet name="03_APIインターフェース" sheetId="4" ns1:id="Rf55b0440415748c1"/>
-    <ns0:sheet name="04_処理業務フロー" sheetId="5" ns1:id="Rf7ae336968ff42ac"/>
-    <ns0:sheet name="05_SQL_Parameter" sheetId="6" ns1:id="R6ecf54ead0c74a56"/>
-    <ns0:sheet name="06_単体テスト観点" sheetId="7" ns1:id="R957b792507654bd0"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R41f99e887b204af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rec6c42366b9e4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R5e57488f049c4d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="Rb7db89e5eedc4c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Ra5801db5c7584f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R543a9943cf94468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="Rfa811b79215846a6"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
@@ -465,7 +468,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="215">
+  <x:cellXfs count="216">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1089,6 +1092,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1857,81 +1863,36 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+    <x:row r="22" ht="85" customHeight="1">
       <x:c r="A22" s="147" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="B22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="C22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="D22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="E22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="F22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="G22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="H22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="I22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="J22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="K22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="L22" s="149" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6を作成根拠として固定）。10 Ver.2.7のAUTH-001契約と照合済。01BのSheet構成、04のStep表を維持。正本参照は02。</x:v>
+      </x:c>
+      <x:c r="B22" s="148"/>
+      <x:c r="C22" s="148"/>
+      <x:c r="D22" s="148"/>
+      <x:c r="E22" s="148"/>
+      <x:c r="F22" s="148"/>
+      <x:c r="G22" s="148"/>
+      <x:c r="H22" s="148"/>
+      <x:c r="I22" s="148"/>
+      <x:c r="J22" s="148"/>
+      <x:c r="K22" s="148"/>
+      <x:c r="L22" s="149"/>
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
-      <x:c r="A23" s="150" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="B23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="C23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="D23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="E23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="F23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="G23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="H23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="I23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="J23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="K23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="L23" s="152" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
+      <x:c r="A23" s="150"/>
+      <x:c r="B23" s="151"/>
+      <x:c r="C23" s="151"/>
+      <x:c r="D23" s="151"/>
+      <x:c r="E23" s="151"/>
+      <x:c r="F23" s="151"/>
+      <x:c r="G23" s="151"/>
+      <x:c r="H23" s="151"/>
+      <x:c r="I23" s="151"/>
+      <x:c r="J23" s="151"/>
+      <x:c r="K23" s="151"/>
+      <x:c r="L23" s="152"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2"/>
@@ -2335,15 +2296,31 @@
       <x:c r="K11" s="156"/>
       <x:c r="L11" s="156"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="156"/>
-      <x:c r="B12" s="156"/>
-      <x:c r="C12" s="156"/>
-      <x:c r="D12" s="156"/>
-      <x:c r="E12" s="156"/>
-      <x:c r="F12" s="156"/>
-      <x:c r="G12" s="156"/>
-      <x:c r="H12" s="156"/>
+    <x:row r="12" ht="84" customHeight="1">
+      <x:c r="A12" s="156" t="str">
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B12" s="215" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C12" s="156" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D12" s="156" t="str">
+        <x:v>二次Review完了。SCR参照版とDB後続成果物参照を整理。Flow・SQL処理・UT変更なし。</x:v>
+      </x:c>
+      <x:c r="E12" s="156" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F12" s="156" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G12" s="156" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H12" s="156" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
       <x:c r="I12" s="156"/>
       <x:c r="J12" s="156"/>
       <x:c r="K12" s="156"/>
@@ -4080,23 +4057,13 @@
         <x:v>適用</x:v>
       </x:c>
       <x:c r="C22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="D22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="E22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="F22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="G22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="H22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（作成根拠：10・16・19 Ver.2.6）。二次Reviewで10 Ver.2.7のAUTH-001契約と整合確認。</x:v>
+      </x:c>
+      <x:c r="D22" s="160"/>
+      <x:c r="E22" s="160"/>
+      <x:c r="F22" s="160"/>
+      <x:c r="G22" s="160"/>
+      <x:c r="H22" s="160"/>
       <x:c r="I22" s="160" t="str">
         <x:v>02権限；03Validation；10API；15DB；16Rule；17TX；18Message；19Security</x:v>
       </x:c>
@@ -4194,23 +4161,13 @@
         <x:v>対応済</x:v>
       </x:c>
       <x:c r="C25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="D25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="E25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="F25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="G25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="H25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
+        <x:v>SCR-001 Ver.2.5はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="D25" s="160"/>
+      <x:c r="E25" s="160"/>
+      <x:c r="F25" s="160"/>
+      <x:c r="G25" s="160"/>
+      <x:c r="H25" s="160"/>
       <x:c r="I25" s="160" t="str">
         <x:v>SCR-001／06・07・08・09。AUTH-4290の本API既定Headerは60。</x:v>
       </x:c>
@@ -5144,13 +5101,11 @@
     <x:mergeCell ref="A20:L20"/>
     <x:mergeCell ref="C21:H21"/>
     <x:mergeCell ref="I21:L21"/>
-    <x:mergeCell ref="C22:H22"/>
     <x:mergeCell ref="I22:L22"/>
     <x:mergeCell ref="C23:H23"/>
     <x:mergeCell ref="I23:L23"/>
     <x:mergeCell ref="C24:H24"/>
     <x:mergeCell ref="I24:L24"/>
-    <x:mergeCell ref="C25:H25"/>
     <x:mergeCell ref="I25:L25"/>
     <x:mergeCell ref="A13:C13"/>
     <x:mergeCell ref="D13:F13"/>
@@ -5167,6 +5122,8 @@
     <x:mergeCell ref="A17:C17"/>
     <x:mergeCell ref="D17:F17"/>
     <x:mergeCell ref="G17:L17"/>
+    <x:mergeCell ref="C22:H22"/>
+    <x:mergeCell ref="C25:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5567,7 +5524,7 @@
         <x:v>関連画面</x:v>
       </x:c>
       <x:c r="B17" s="73" t="str">
-        <x:v>SCR-001 Ver.2.4</x:v>
+        <x:v>SCR-001 Ver.2.5</x:v>
       </x:c>
       <x:c r="C17" s="73" t="str">
         <x:v>画面詳細設計／01_SCR-001</x:v>
@@ -12218,7 +12175,7 @@
       </x:c>
       <x:c r="L28" s="2"/>
     </x:row>
-    <x:row r="29" ht="90" hidden="0" customHeight="1">
+    <x:row r="29" ht="75" hidden="0" customHeight="1">
       <x:c r="A29" s="73" t="str">
         <x:v>SQL-07</x:v>
       </x:c>
@@ -12241,7 +12198,7 @@
         <x:v>DB IDENTITY採番</x:v>
       </x:c>
       <x:c r="H29" s="73" t="str">
-        <x:v>03_DB-DD-03／20_login_histories参照</x:v>
+        <x:v>15_DB基本設計書／07_Column定義（login_histories.id）。採番は本書SQL-07。DB-DD-03は後続作成対象。</x:v>
       </x:c>
       <x:c r="I29" s="73" t="str">
         <x:v>PK</x:v>
@@ -17442,773 +17399,131 @@
 INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
 VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
 RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+-- idはDB IDENTITY採番（本書SQL-07の採番定義。DB-DD-03は後続作成対象）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B99" s="172"/>
+      <x:c r="C99" s="172"/>
+      <x:c r="D99" s="172"/>
+      <x:c r="E99" s="172"/>
+      <x:c r="F99" s="172"/>
+      <x:c r="G99" s="172"/>
+      <x:c r="H99" s="172"/>
+      <x:c r="I99" s="172"/>
+      <x:c r="J99" s="172"/>
+      <x:c r="K99" s="172"/>
+      <x:c r="L99" s="172"/>
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
-      <x:c r="A100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A100" s="172"/>
+      <x:c r="B100" s="172"/>
+      <x:c r="C100" s="172"/>
+      <x:c r="D100" s="172"/>
+      <x:c r="E100" s="172"/>
+      <x:c r="F100" s="172"/>
+      <x:c r="G100" s="172"/>
+      <x:c r="H100" s="172"/>
+      <x:c r="I100" s="172"/>
+      <x:c r="J100" s="172"/>
+      <x:c r="K100" s="172"/>
+      <x:c r="L100" s="172"/>
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
-      <x:c r="A101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A101" s="196"/>
+      <x:c r="B101" s="196"/>
+      <x:c r="C101" s="196"/>
+      <x:c r="D101" s="196"/>
+      <x:c r="E101" s="196"/>
+      <x:c r="F101" s="196"/>
+      <x:c r="G101" s="196"/>
+      <x:c r="H101" s="196"/>
+      <x:c r="I101" s="196"/>
+      <x:c r="J101" s="196"/>
+      <x:c r="K101" s="196"/>
+      <x:c r="L101" s="196"/>
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
-      <x:c r="A102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A102" s="196"/>
+      <x:c r="B102" s="196"/>
+      <x:c r="C102" s="196"/>
+      <x:c r="D102" s="196"/>
+      <x:c r="E102" s="196"/>
+      <x:c r="F102" s="196"/>
+      <x:c r="G102" s="196"/>
+      <x:c r="H102" s="196"/>
+      <x:c r="I102" s="196"/>
+      <x:c r="J102" s="196"/>
+      <x:c r="K102" s="196"/>
+      <x:c r="L102" s="196"/>
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
-      <x:c r="A103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A103" s="196"/>
+      <x:c r="B103" s="196"/>
+      <x:c r="C103" s="196"/>
+      <x:c r="D103" s="196"/>
+      <x:c r="E103" s="196"/>
+      <x:c r="F103" s="196"/>
+      <x:c r="G103" s="196"/>
+      <x:c r="H103" s="196"/>
+      <x:c r="I103" s="196"/>
+      <x:c r="J103" s="196"/>
+      <x:c r="K103" s="196"/>
+      <x:c r="L103" s="196"/>
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
-      <x:c r="A104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A104" s="196"/>
+      <x:c r="B104" s="196"/>
+      <x:c r="C104" s="196"/>
+      <x:c r="D104" s="196"/>
+      <x:c r="E104" s="196"/>
+      <x:c r="F104" s="196"/>
+      <x:c r="G104" s="196"/>
+      <x:c r="H104" s="196"/>
+      <x:c r="I104" s="196"/>
+      <x:c r="J104" s="196"/>
+      <x:c r="K104" s="196"/>
+      <x:c r="L104" s="196"/>
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
-      <x:c r="A105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A105" s="196"/>
+      <x:c r="B105" s="196"/>
+      <x:c r="C105" s="196"/>
+      <x:c r="D105" s="196"/>
+      <x:c r="E105" s="196"/>
+      <x:c r="F105" s="196"/>
+      <x:c r="G105" s="196"/>
+      <x:c r="H105" s="196"/>
+      <x:c r="I105" s="196"/>
+      <x:c r="J105" s="196"/>
+      <x:c r="K105" s="196"/>
+      <x:c r="L105" s="196"/>
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
-      <x:c r="A106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A106" s="196"/>
+      <x:c r="B106" s="196"/>
+      <x:c r="C106" s="196"/>
+      <x:c r="D106" s="196"/>
+      <x:c r="E106" s="196"/>
+      <x:c r="F106" s="196"/>
+      <x:c r="G106" s="196"/>
+      <x:c r="H106" s="196"/>
+      <x:c r="I106" s="196"/>
+      <x:c r="J106" s="196"/>
+      <x:c r="K106" s="196"/>
+      <x:c r="L106" s="196"/>
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
-      <x:c r="A107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A107" s="196"/>
+      <x:c r="B107" s="196"/>
+      <x:c r="C107" s="196"/>
+      <x:c r="D107" s="196"/>
+      <x:c r="E107" s="196"/>
+      <x:c r="F107" s="196"/>
+      <x:c r="G107" s="196"/>
+      <x:c r="H107" s="196"/>
+      <x:c r="I107" s="196"/>
+      <x:c r="J107" s="196"/>
+      <x:c r="K107" s="196"/>
+      <x:c r="L107" s="196"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
+++ b/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R41f99e887b204af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rec6c42366b9e4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R5e57488f049c4d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="Rb7db89e5eedc4c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Ra5801db5c7584f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R543a9943cf94468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="Rfa811b79215846a6"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rbd362f6addd44026"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R9eb53fffc9064d4d"/>
+    <ns0:sheet name="02_API一覧" sheetId="3" ns1:id="R86e00ae799ef494d"/>
+    <ns0:sheet name="03_APIインターフェース" sheetId="4" ns1:id="Rf55b0440415748c1"/>
+    <ns0:sheet name="04_処理業務フロー" sheetId="5" ns1:id="Rf7ae336968ff42ac"/>
+    <ns0:sheet name="05_SQL_Parameter" sheetId="6" ns1:id="R6ecf54ead0c74a56"/>
+    <ns0:sheet name="06_単体テスト観点" sheetId="7" ns1:id="R957b792507654bd0"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,9 +19,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </x:numFmts>
   <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
@@ -468,7 +465,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="216">
+  <x:cellXfs count="215">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1094,9 +1091,6 @@
     <x:xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1863,36 +1857,81 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="85" customHeight="1">
+    <x:row r="22" ht="40" customHeight="1">
       <x:c r="A22" s="147" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
-参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6を作成根拠として固定）。10 Ver.2.7のAUTH-001契約と照合済。01BのSheet構成、04のStep表を維持。正本参照は02。</x:v>
-      </x:c>
-      <x:c r="B22" s="148"/>
-      <x:c r="C22" s="148"/>
-      <x:c r="D22" s="148"/>
-      <x:c r="E22" s="148"/>
-      <x:c r="F22" s="148"/>
-      <x:c r="G22" s="148"/>
-      <x:c r="H22" s="148"/>
-      <x:c r="I22" s="148"/>
-      <x:c r="J22" s="148"/>
-      <x:c r="K22" s="148"/>
-      <x:c r="L22" s="149"/>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="B22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="C22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="D22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="E22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="F22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="G22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="H22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="I22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="J22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="K22" s="148" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="L22" s="149" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
-      <x:c r="A23" s="150"/>
-      <x:c r="B23" s="151"/>
-      <x:c r="C23" s="151"/>
-      <x:c r="D23" s="151"/>
-      <x:c r="E23" s="151"/>
-      <x:c r="F23" s="151"/>
-      <x:c r="G23" s="151"/>
-      <x:c r="H23" s="151"/>
-      <x:c r="I23" s="151"/>
-      <x:c r="J23" s="151"/>
-      <x:c r="K23" s="151"/>
-      <x:c r="L23" s="152"/>
+      <x:c r="A23" s="150" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="B23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="C23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="D23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="E23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="F23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="G23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="H23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="I23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="J23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="K23" s="151" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
+      <x:c r="L23" s="152" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2"/>
@@ -2296,31 +2335,15 @@
       <x:c r="K11" s="156"/>
       <x:c r="L11" s="156"/>
     </x:row>
-    <x:row r="12" ht="84" customHeight="1">
-      <x:c r="A12" s="156" t="str">
-        <x:v>Ver.2.2</x:v>
-      </x:c>
-      <x:c r="B12" s="215" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="C12" s="156" t="str">
-        <x:v>Review</x:v>
-      </x:c>
-      <x:c r="D12" s="156" t="str">
-        <x:v>二次Review完了。SCR参照版とDB後続成果物参照を整理。Flow・SQL処理・UT変更なし。</x:v>
-      </x:c>
-      <x:c r="E12" s="156" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="F12" s="156" t="str">
-        <x:v>Review済</x:v>
-      </x:c>
-      <x:c r="G12" s="156" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="H12" s="156" t="str">
-        <x:v>承認待ち</x:v>
-      </x:c>
+    <x:row r="12">
+      <x:c r="A12" s="156"/>
+      <x:c r="B12" s="156"/>
+      <x:c r="C12" s="156"/>
+      <x:c r="D12" s="156"/>
+      <x:c r="E12" s="156"/>
+      <x:c r="F12" s="156"/>
+      <x:c r="G12" s="156"/>
+      <x:c r="H12" s="156"/>
       <x:c r="I12" s="156"/>
       <x:c r="J12" s="156"/>
       <x:c r="K12" s="156"/>
@@ -4057,13 +4080,23 @@
         <x:v>適用</x:v>
       </x:c>
       <x:c r="C22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（作成根拠：10・16・19 Ver.2.6）。二次Reviewで10 Ver.2.7のAUTH-001契約と整合確認。</x:v>
-      </x:c>
-      <x:c r="D22" s="160"/>
-      <x:c r="E22" s="160"/>
-      <x:c r="F22" s="160"/>
-      <x:c r="G22" s="160"/>
-      <x:c r="H22" s="160"/>
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
+      <x:c r="D22" s="160" t="str">
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
+      <x:c r="E22" s="160" t="str">
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
+      <x:c r="F22" s="160" t="str">
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
+      <x:c r="G22" s="160" t="str">
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
+      <x:c r="H22" s="160" t="str">
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
+      </x:c>
       <x:c r="I22" s="160" t="str">
         <x:v>02権限；03Validation；10API；15DB；16Rule；17TX；18Message；19Security</x:v>
       </x:c>
@@ -4161,13 +4194,23 @@
         <x:v>対応済</x:v>
       </x:c>
       <x:c r="C25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.5はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="D25" s="160"/>
-      <x:c r="E25" s="160"/>
-      <x:c r="F25" s="160"/>
-      <x:c r="G25" s="160"/>
-      <x:c r="H25" s="160"/>
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="D25" s="160" t="str">
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="E25" s="160" t="str">
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="F25" s="160" t="str">
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="G25" s="160" t="str">
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="H25" s="160" t="str">
+        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
       <x:c r="I25" s="160" t="str">
         <x:v>SCR-001／06・07・08・09。AUTH-4290の本API既定Headerは60。</x:v>
       </x:c>
@@ -5101,11 +5144,13 @@
     <x:mergeCell ref="A20:L20"/>
     <x:mergeCell ref="C21:H21"/>
     <x:mergeCell ref="I21:L21"/>
+    <x:mergeCell ref="C22:H22"/>
     <x:mergeCell ref="I22:L22"/>
     <x:mergeCell ref="C23:H23"/>
     <x:mergeCell ref="I23:L23"/>
     <x:mergeCell ref="C24:H24"/>
     <x:mergeCell ref="I24:L24"/>
+    <x:mergeCell ref="C25:H25"/>
     <x:mergeCell ref="I25:L25"/>
     <x:mergeCell ref="A13:C13"/>
     <x:mergeCell ref="D13:F13"/>
@@ -5122,8 +5167,6 @@
     <x:mergeCell ref="A17:C17"/>
     <x:mergeCell ref="D17:F17"/>
     <x:mergeCell ref="G17:L17"/>
-    <x:mergeCell ref="C22:H22"/>
-    <x:mergeCell ref="C25:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5524,7 +5567,7 @@
         <x:v>関連画面</x:v>
       </x:c>
       <x:c r="B17" s="73" t="str">
-        <x:v>SCR-001 Ver.2.5</x:v>
+        <x:v>SCR-001 Ver.2.4</x:v>
       </x:c>
       <x:c r="C17" s="73" t="str">
         <x:v>画面詳細設計／01_SCR-001</x:v>
@@ -12175,7 +12218,7 @@
       </x:c>
       <x:c r="L28" s="2"/>
     </x:row>
-    <x:row r="29" ht="75" hidden="0" customHeight="1">
+    <x:row r="29" ht="90" hidden="0" customHeight="1">
       <x:c r="A29" s="73" t="str">
         <x:v>SQL-07</x:v>
       </x:c>
@@ -12198,7 +12241,7 @@
         <x:v>DB IDENTITY採番</x:v>
       </x:c>
       <x:c r="H29" s="73" t="str">
-        <x:v>15_DB基本設計書／07_Column定義（login_histories.id）。採番は本書SQL-07。DB-DD-03は後続作成対象。</x:v>
+        <x:v>03_DB-DD-03／20_login_histories参照</x:v>
       </x:c>
       <x:c r="I29" s="73" t="str">
         <x:v>PK</x:v>
@@ -17399,131 +17442,773 @@
 INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
 VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
 RETURNING id;
--- idはDB IDENTITY採番（本書SQL-07の採番定義。DB-DD-03は後続作成対象）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B99" s="172"/>
-      <x:c r="C99" s="172"/>
-      <x:c r="D99" s="172"/>
-      <x:c r="E99" s="172"/>
-      <x:c r="F99" s="172"/>
-      <x:c r="G99" s="172"/>
-      <x:c r="H99" s="172"/>
-      <x:c r="I99" s="172"/>
-      <x:c r="J99" s="172"/>
-      <x:c r="K99" s="172"/>
-      <x:c r="L99" s="172"/>
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L99" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
-      <x:c r="A100" s="172"/>
-      <x:c r="B100" s="172"/>
-      <x:c r="C100" s="172"/>
-      <x:c r="D100" s="172"/>
-      <x:c r="E100" s="172"/>
-      <x:c r="F100" s="172"/>
-      <x:c r="G100" s="172"/>
-      <x:c r="H100" s="172"/>
-      <x:c r="I100" s="172"/>
-      <x:c r="J100" s="172"/>
-      <x:c r="K100" s="172"/>
-      <x:c r="L100" s="172"/>
+      <x:c r="A100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L100" s="172" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
-      <x:c r="A101" s="196"/>
-      <x:c r="B101" s="196"/>
-      <x:c r="C101" s="196"/>
-      <x:c r="D101" s="196"/>
-      <x:c r="E101" s="196"/>
-      <x:c r="F101" s="196"/>
-      <x:c r="G101" s="196"/>
-      <x:c r="H101" s="196"/>
-      <x:c r="I101" s="196"/>
-      <x:c r="J101" s="196"/>
-      <x:c r="K101" s="196"/>
-      <x:c r="L101" s="196"/>
+      <x:c r="A101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L101" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
-      <x:c r="A102" s="196"/>
-      <x:c r="B102" s="196"/>
-      <x:c r="C102" s="196"/>
-      <x:c r="D102" s="196"/>
-      <x:c r="E102" s="196"/>
-      <x:c r="F102" s="196"/>
-      <x:c r="G102" s="196"/>
-      <x:c r="H102" s="196"/>
-      <x:c r="I102" s="196"/>
-      <x:c r="J102" s="196"/>
-      <x:c r="K102" s="196"/>
-      <x:c r="L102" s="196"/>
+      <x:c r="A102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L102" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
-      <x:c r="A103" s="196"/>
-      <x:c r="B103" s="196"/>
-      <x:c r="C103" s="196"/>
-      <x:c r="D103" s="196"/>
-      <x:c r="E103" s="196"/>
-      <x:c r="F103" s="196"/>
-      <x:c r="G103" s="196"/>
-      <x:c r="H103" s="196"/>
-      <x:c r="I103" s="196"/>
-      <x:c r="J103" s="196"/>
-      <x:c r="K103" s="196"/>
-      <x:c r="L103" s="196"/>
+      <x:c r="A103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L103" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
-      <x:c r="A104" s="196"/>
-      <x:c r="B104" s="196"/>
-      <x:c r="C104" s="196"/>
-      <x:c r="D104" s="196"/>
-      <x:c r="E104" s="196"/>
-      <x:c r="F104" s="196"/>
-      <x:c r="G104" s="196"/>
-      <x:c r="H104" s="196"/>
-      <x:c r="I104" s="196"/>
-      <x:c r="J104" s="196"/>
-      <x:c r="K104" s="196"/>
-      <x:c r="L104" s="196"/>
+      <x:c r="A104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L104" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
-      <x:c r="A105" s="196"/>
-      <x:c r="B105" s="196"/>
-      <x:c r="C105" s="196"/>
-      <x:c r="D105" s="196"/>
-      <x:c r="E105" s="196"/>
-      <x:c r="F105" s="196"/>
-      <x:c r="G105" s="196"/>
-      <x:c r="H105" s="196"/>
-      <x:c r="I105" s="196"/>
-      <x:c r="J105" s="196"/>
-      <x:c r="K105" s="196"/>
-      <x:c r="L105" s="196"/>
+      <x:c r="A105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L105" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
-      <x:c r="A106" s="196"/>
-      <x:c r="B106" s="196"/>
-      <x:c r="C106" s="196"/>
-      <x:c r="D106" s="196"/>
-      <x:c r="E106" s="196"/>
-      <x:c r="F106" s="196"/>
-      <x:c r="G106" s="196"/>
-      <x:c r="H106" s="196"/>
-      <x:c r="I106" s="196"/>
-      <x:c r="J106" s="196"/>
-      <x:c r="K106" s="196"/>
-      <x:c r="L106" s="196"/>
+      <x:c r="A106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L106" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
-      <x:c r="A107" s="196"/>
-      <x:c r="B107" s="196"/>
-      <x:c r="C107" s="196"/>
-      <x:c r="D107" s="196"/>
-      <x:c r="E107" s="196"/>
-      <x:c r="F107" s="196"/>
-      <x:c r="G107" s="196"/>
-      <x:c r="H107" s="196"/>
-      <x:c r="I107" s="196"/>
-      <x:c r="J107" s="196"/>
-      <x:c r="K107" s="196"/>
-      <x:c r="L107" s="196"/>
+      <x:c r="A107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="C107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="D107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="E107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="F107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="G107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="H107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="I107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="J107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="K107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="L107" s="196" t="str">
+        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
+INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
+VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
+RETURNING id;
+-- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
+++ b/詳細設計/API詳細設計/001_API-AUTH-001_ログインAPI詳細設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9cdab296632f4a21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R55f0903a45bb41ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R7374c81f92a346ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="Rfd8aa52aca1b43b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Rdc5b23efd3f649e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="Re7e4137e90604ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="Rd86ac98797d642b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R41f99e887b204af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rec6c42366b9e4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R5e57488f049c4d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="Rb7db89e5eedc4c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Ra5801db5c7584f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R543a9943cf94468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="Rfa811b79215846a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="21">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -133,6 +136,11 @@
       <x:sz val="11"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172B40"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
   <x:fills count="12">
     <x:fill>
@@ -192,7 +200,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="32">
+  <x:borders count="33">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -442,11 +450,25 @@
         <x:color rgb="FFD9E2F3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="213">
+  <x:cellXfs count="216">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,6 +1088,15 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1687,7 +1718,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="F15" s="146" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="G15" s="146" t="str">
         <x:v>Ver.2.1</x:v>
@@ -1717,7 +1748,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="F16" s="146" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="G16" s="146" t="str">
         <x:v>2026-09-28</x:v>
@@ -1832,81 +1863,36 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+    <x:row r="22" ht="85" customHeight="1">
       <x:c r="A22" s="147" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="B22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="C22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="D22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="E22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="F22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="G22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="H22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="I22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="J22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="K22" s="148" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="L22" s="149" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6を作成根拠として固定）。10 Ver.2.7のAUTH-001契約と照合済。01BのSheet構成、04のStep表を維持。正本参照は02。</x:v>
+      </x:c>
+      <x:c r="B22" s="148"/>
+      <x:c r="C22" s="148"/>
+      <x:c r="D22" s="148"/>
+      <x:c r="E22" s="148"/>
+      <x:c r="F22" s="148"/>
+      <x:c r="G22" s="148"/>
+      <x:c r="H22" s="148"/>
+      <x:c r="I22" s="148"/>
+      <x:c r="J22" s="148"/>
+      <x:c r="K22" s="148"/>
+      <x:c r="L22" s="149"/>
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
-      <x:c r="A23" s="150" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="B23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="C23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="D23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="E23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="F23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="G23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="H23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="I23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="J23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="K23" s="151" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
-      <x:c r="L23" s="152" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。01BテンプレートのSheet構成を維持し、04はReview指示によりStep表へ変更。状態：修正済（承認前）。決定記録は01、正本参照は02。</x:v>
-      </x:c>
+      <x:c r="A23" s="150"/>
+      <x:c r="B23" s="151"/>
+      <x:c r="C23" s="151"/>
+      <x:c r="D23" s="151"/>
+      <x:c r="E23" s="151"/>
+      <x:c r="F23" s="151"/>
+      <x:c r="G23" s="151"/>
+      <x:c r="H23" s="151"/>
+      <x:c r="I23" s="151"/>
+      <x:c r="J23" s="151"/>
+      <x:c r="K23" s="151"/>
+      <x:c r="L23" s="152"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2"/>
@@ -2085,7 +2071,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -2280,29 +2266,61 @@
       <x:c r="K10" s="156"/>
       <x:c r="L10" s="156"/>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="156"/>
-      <x:c r="B11" s="156"/>
-      <x:c r="C11" s="156"/>
-      <x:c r="D11" s="156"/>
-      <x:c r="E11" s="156"/>
-      <x:c r="F11" s="156"/>
-      <x:c r="G11" s="156"/>
-      <x:c r="H11" s="156"/>
+    <x:row r="11" ht="75" customHeight="1">
+      <x:c r="A11" s="214" t="str">
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B11" s="214" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C11" s="214" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D11" s="214" t="str">
+        <x:v>CHG-DB-20260929-01：参照Columnの注記を物理外鍵なしへ統一。認証処理/SQL/応答契約は変更なし。</x:v>
+      </x:c>
+      <x:c r="E11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G11" s="214" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H11" s="214" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
       <x:c r="I11" s="156"/>
       <x:c r="J11" s="156"/>
       <x:c r="K11" s="156"/>
       <x:c r="L11" s="156"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="156"/>
-      <x:c r="B12" s="156"/>
-      <x:c r="C12" s="156"/>
-      <x:c r="D12" s="156"/>
-      <x:c r="E12" s="156"/>
-      <x:c r="F12" s="156"/>
-      <x:c r="G12" s="156"/>
-      <x:c r="H12" s="156"/>
+    <x:row r="12" ht="84" customHeight="1">
+      <x:c r="A12" s="156" t="str">
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B12" s="215" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C12" s="156" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D12" s="156" t="str">
+        <x:v>二次Review完了。SCR参照版とDB後続成果物参照を整理。Flow・SQL処理・UT変更なし。</x:v>
+      </x:c>
+      <x:c r="E12" s="156" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F12" s="156" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G12" s="156" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H12" s="156" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
       <x:c r="I12" s="156"/>
       <x:c r="J12" s="156"/>
       <x:c r="K12" s="156"/>
@@ -3496,7 +3514,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -4039,23 +4057,13 @@
         <x:v>適用</x:v>
       </x:c>
       <x:c r="C22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="D22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="E22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="F22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="G22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
-      <x:c r="H22" s="160" t="str">
-        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）</x:v>
-      </x:c>
+        <x:v>BL-2026-09-24＋CHG-AUTH-20260928-01（作成根拠：10・16・19 Ver.2.6）。二次Reviewで10 Ver.2.7のAUTH-001契約と整合確認。</x:v>
+      </x:c>
+      <x:c r="D22" s="160"/>
+      <x:c r="E22" s="160"/>
+      <x:c r="F22" s="160"/>
+      <x:c r="G22" s="160"/>
+      <x:c r="H22" s="160"/>
       <x:c r="I22" s="160" t="str">
         <x:v>02権限；03Validation；10API；15DB；16Rule；17TX；18Message；19Security</x:v>
       </x:c>
@@ -4153,23 +4161,13 @@
         <x:v>対応済</x:v>
       </x:c>
       <x:c r="C25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="D25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="E25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="F25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="G25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
-      <x:c r="H25" s="160" t="str">
-        <x:v>SCR-001 Ver.2.4はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
-      </x:c>
+        <x:v>SCR-001 Ver.2.5はRetry-After=0を有効・待機不要として処理。Message・Focus・UTまで整合。</x:v>
+      </x:c>
+      <x:c r="D25" s="160"/>
+      <x:c r="E25" s="160"/>
+      <x:c r="F25" s="160"/>
+      <x:c r="G25" s="160"/>
+      <x:c r="H25" s="160"/>
       <x:c r="I25" s="160" t="str">
         <x:v>SCR-001／06・07・08・09。AUTH-4290の本API既定Headerは60。</x:v>
       </x:c>
@@ -5103,13 +5101,11 @@
     <x:mergeCell ref="A20:L20"/>
     <x:mergeCell ref="C21:H21"/>
     <x:mergeCell ref="I21:L21"/>
-    <x:mergeCell ref="C22:H22"/>
     <x:mergeCell ref="I22:L22"/>
     <x:mergeCell ref="C23:H23"/>
     <x:mergeCell ref="I23:L23"/>
     <x:mergeCell ref="C24:H24"/>
     <x:mergeCell ref="I24:L24"/>
-    <x:mergeCell ref="C25:H25"/>
     <x:mergeCell ref="I25:L25"/>
     <x:mergeCell ref="A13:C13"/>
     <x:mergeCell ref="D13:F13"/>
@@ -5126,6 +5122,8 @@
     <x:mergeCell ref="A17:C17"/>
     <x:mergeCell ref="D17:F17"/>
     <x:mergeCell ref="G17:L17"/>
+    <x:mergeCell ref="C22:H22"/>
+    <x:mergeCell ref="C25:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5216,7 +5214,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -5526,7 +5524,7 @@
         <x:v>関連画面</x:v>
       </x:c>
       <x:c r="B17" s="73" t="str">
-        <x:v>SCR-001 Ver.2.4</x:v>
+        <x:v>SCR-001 Ver.2.5</x:v>
       </x:c>
       <x:c r="C17" s="73" t="str">
         <x:v>画面詳細設計／01_SCR-001</x:v>
@@ -8263,7 +8261,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -11372,7 +11370,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
@@ -12023,7 +12021,7 @@
         <x:v>同一Transaction</x:v>
       </x:c>
       <x:c r="I24" s="73" t="str">
-        <x:v>user_roles.user_id等FK/UK</x:v>
+        <x:v>user_roles.user_id等の論理参照/UK</x:v>
       </x:c>
       <x:c r="J24" s="73" t="str">
         <x:v>認証対象User</x:v>
@@ -12177,7 +12175,7 @@
       </x:c>
       <x:c r="L28" s="2"/>
     </x:row>
-    <x:row r="29" ht="90" hidden="0" customHeight="1">
+    <x:row r="29" ht="75" hidden="0" customHeight="1">
       <x:c r="A29" s="73" t="str">
         <x:v>SQL-07</x:v>
       </x:c>
@@ -12200,7 +12198,7 @@
         <x:v>DB IDENTITY採番</x:v>
       </x:c>
       <x:c r="H29" s="73" t="str">
-        <x:v>03_DB-DD-03／20_login_histories参照</x:v>
+        <x:v>15_DB基本設計書／07_Column定義（login_histories.id）。採番は本書SQL-07。DB-DD-03は後続作成対象。</x:v>
       </x:c>
       <x:c r="I29" s="73" t="str">
         <x:v>PK</x:v>
@@ -12213,7 +12211,7 @@
       </x:c>
       <x:c r="L29" s="2"/>
     </x:row>
-    <x:row r="30" ht="90" hidden="0" customHeight="1">
+    <x:row r="30" ht="65" hidden="0" customHeight="1">
       <x:c r="A30" s="73" t="str">
         <x:v>SQL-07</x:v>
       </x:c>
@@ -12236,10 +12234,10 @@
         <x:v>SQL-01.id、不存在はnull</x:v>
       </x:c>
       <x:c r="H30" s="73" t="str">
-        <x:v>存在しないUserのFK値を捏造しない</x:v>
+        <x:v>存在しないUser IDを記録しない。取得できない場合はNULL。</x:v>
       </x:c>
       <x:c r="I30" s="73" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照（物理外鍵なし）</x:v>
       </x:c>
       <x:c r="J30" s="73" t="str">
         <x:v>認証対象</x:v>
@@ -17401,773 +17399,131 @@
 INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
 VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
 RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L99" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+-- idはDB IDENTITY採番（本書SQL-07の採番定義。DB-DD-03は後続作成対象）。通常拒否のFAILUREもCommit。</x:v>
+      </x:c>
+      <x:c r="B99" s="172"/>
+      <x:c r="C99" s="172"/>
+      <x:c r="D99" s="172"/>
+      <x:c r="E99" s="172"/>
+      <x:c r="F99" s="172"/>
+      <x:c r="G99" s="172"/>
+      <x:c r="H99" s="172"/>
+      <x:c r="I99" s="172"/>
+      <x:c r="J99" s="172"/>
+      <x:c r="K99" s="172"/>
+      <x:c r="L99" s="172"/>
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
-      <x:c r="A100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L100" s="172" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A100" s="172"/>
+      <x:c r="B100" s="172"/>
+      <x:c r="C100" s="172"/>
+      <x:c r="D100" s="172"/>
+      <x:c r="E100" s="172"/>
+      <x:c r="F100" s="172"/>
+      <x:c r="G100" s="172"/>
+      <x:c r="H100" s="172"/>
+      <x:c r="I100" s="172"/>
+      <x:c r="J100" s="172"/>
+      <x:c r="K100" s="172"/>
+      <x:c r="L100" s="172"/>
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
-      <x:c r="A101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L101" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A101" s="196"/>
+      <x:c r="B101" s="196"/>
+      <x:c r="C101" s="196"/>
+      <x:c r="D101" s="196"/>
+      <x:c r="E101" s="196"/>
+      <x:c r="F101" s="196"/>
+      <x:c r="G101" s="196"/>
+      <x:c r="H101" s="196"/>
+      <x:c r="I101" s="196"/>
+      <x:c r="J101" s="196"/>
+      <x:c r="K101" s="196"/>
+      <x:c r="L101" s="196"/>
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
-      <x:c r="A102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L102" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A102" s="196"/>
+      <x:c r="B102" s="196"/>
+      <x:c r="C102" s="196"/>
+      <x:c r="D102" s="196"/>
+      <x:c r="E102" s="196"/>
+      <x:c r="F102" s="196"/>
+      <x:c r="G102" s="196"/>
+      <x:c r="H102" s="196"/>
+      <x:c r="I102" s="196"/>
+      <x:c r="J102" s="196"/>
+      <x:c r="K102" s="196"/>
+      <x:c r="L102" s="196"/>
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
-      <x:c r="A103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L103" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A103" s="196"/>
+      <x:c r="B103" s="196"/>
+      <x:c r="C103" s="196"/>
+      <x:c r="D103" s="196"/>
+      <x:c r="E103" s="196"/>
+      <x:c r="F103" s="196"/>
+      <x:c r="G103" s="196"/>
+      <x:c r="H103" s="196"/>
+      <x:c r="I103" s="196"/>
+      <x:c r="J103" s="196"/>
+      <x:c r="K103" s="196"/>
+      <x:c r="L103" s="196"/>
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
-      <x:c r="A104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L104" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A104" s="196"/>
+      <x:c r="B104" s="196"/>
+      <x:c r="C104" s="196"/>
+      <x:c r="D104" s="196"/>
+      <x:c r="E104" s="196"/>
+      <x:c r="F104" s="196"/>
+      <x:c r="G104" s="196"/>
+      <x:c r="H104" s="196"/>
+      <x:c r="I104" s="196"/>
+      <x:c r="J104" s="196"/>
+      <x:c r="K104" s="196"/>
+      <x:c r="L104" s="196"/>
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
-      <x:c r="A105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L105" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A105" s="196"/>
+      <x:c r="B105" s="196"/>
+      <x:c r="C105" s="196"/>
+      <x:c r="D105" s="196"/>
+      <x:c r="E105" s="196"/>
+      <x:c r="F105" s="196"/>
+      <x:c r="G105" s="196"/>
+      <x:c r="H105" s="196"/>
+      <x:c r="I105" s="196"/>
+      <x:c r="J105" s="196"/>
+      <x:c r="K105" s="196"/>
+      <x:c r="L105" s="196"/>
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
-      <x:c r="A106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L106" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A106" s="196"/>
+      <x:c r="B106" s="196"/>
+      <x:c r="C106" s="196"/>
+      <x:c r="D106" s="196"/>
+      <x:c r="E106" s="196"/>
+      <x:c r="F106" s="196"/>
+      <x:c r="G106" s="196"/>
+      <x:c r="H106" s="196"/>
+      <x:c r="I106" s="196"/>
+      <x:c r="J106" s="196"/>
+      <x:c r="K106" s="196"/>
+      <x:c r="L106" s="196"/>
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
-      <x:c r="A107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="B107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="C107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="D107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="E107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="F107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="G107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="H107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="I107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="J107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="K107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
-      <x:c r="L107" s="196" t="str">
-        <x:v>-- SQL-07 / Step11 / 1件必須。userIdは不存在時NULL
-INSERT INTO login_histories(user_id,username,result,ip_address,user_agent,created_at)
-VALUES(:userId,:username,:result,:ipAddress,:userAgent,:now)
-RETURNING id;
--- idはDB IDENTITY採番（03_DB-DD-03／20_login_histories）。通常拒否のFAILUREもCommit。</x:v>
-      </x:c>
+      <x:c r="A107" s="196"/>
+      <x:c r="B107" s="196"/>
+      <x:c r="C107" s="196"/>
+      <x:c r="D107" s="196"/>
+      <x:c r="E107" s="196"/>
+      <x:c r="F107" s="196"/>
+      <x:c r="G107" s="196"/>
+      <x:c r="H107" s="196"/>
+      <x:c r="I107" s="196"/>
+      <x:c r="J107" s="196"/>
+      <x:c r="K107" s="196"/>
+      <x:c r="L107" s="196"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -18275,7 +17631,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.1</x:v>
+        <x:v>Ver.2.2</x:v>
       </x:c>
       <x:c r="K2" s="61" t="str">
         <x:v>Ver.2.1</x:v>
